--- a/cls.var_AMR_EHPAD_C3G_R.xlsx
+++ b/cls.var_AMR_EHPAD_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cluster_4</t>
   </si>
   <si>
     <t xml:space="preserve">tx_possession_chevaux</t>
@@ -651,12 +648,12 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -664,15 +661,15 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -680,7 +677,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -688,7 +685,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -696,7 +693,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -704,7 +701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -712,7 +709,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -720,7 +717,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -728,7 +725,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -736,7 +733,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -744,7 +741,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -752,7 +749,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -760,7 +757,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
@@ -768,7 +765,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -776,7 +773,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
@@ -784,7 +781,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -792,7 +789,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
@@ -800,7 +797,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
